--- a/artfynd/A 22566-2022 artfynd.xlsx
+++ b/artfynd/A 22566-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22566-2022 artfynd.xlsx
+++ b/artfynd/A 22566-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1121,6 +1121,127 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120193279</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96862</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Revlummer, Näsvattnet, Sättna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>595223</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6928170</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anna Silverliv</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anna Silverliv</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22566-2022 artfynd.xlsx
+++ b/artfynd/A 22566-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1121,127 +1121,6 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>120193279</v>
-      </c>
-      <c r="B6" t="n">
-        <v>96862</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Revlummer, Näsvattnet, Sättna, Mpd</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>595223</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6928170</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Sundsvall</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Sättna</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Anna Silverliv</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Anna Silverliv</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22566-2022 artfynd.xlsx
+++ b/artfynd/A 22566-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1121,6 +1121,118 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124125770</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tretå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>595082</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6928165</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Tretå som satt och trummade.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22566-2022 artfynd.xlsx
+++ b/artfynd/A 22566-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105899141</v>
+        <v>105899135</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594892.3386079179</v>
+        <v>594793</v>
       </c>
       <c r="R2" t="n">
-        <v>6928210.600846382</v>
+        <v>6928208</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2022-09-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105899135</v>
+        <v>105899136</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594792.2895878622</v>
+        <v>594825</v>
       </c>
       <c r="R3" t="n">
-        <v>6928208.676944239</v>
+        <v>6928208</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2022-09-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105899136</v>
+        <v>105899137</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594825.6831525806</v>
+        <v>594937</v>
       </c>
       <c r="R4" t="n">
-        <v>6928207.776569455</v>
+        <v>6928221</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +937,9 @@
           <t>2022-09-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,53 +966,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105899137</v>
+        <v>124224661</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjärdalsberget, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594937.4555997774</v>
+        <v>595246</v>
       </c>
       <c r="R5" t="n">
-        <v>6928221.142335609</v>
+        <v>6928160</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1036,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,12 +1056,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Dennis Jonason</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Dennis Jonason</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1126,12 +1071,7 @@
         <v>124125770</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,6 +1172,215 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>105899141</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tjärdalsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>594893</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6928211</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Dennis Jonason</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Dennis Jonason</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120198161</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Revlummer, Näsvattnet, Sättna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>595184</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6928125</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anna Silverliv</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anna Silverliv</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22566-2022 artfynd.xlsx
+++ b/artfynd/A 22566-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105899135</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105899136</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105899137</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124224661</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124125770</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1269,6 +1299,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105899141</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,8 +1416,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120198161</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>